--- a/experiment/SRForm2_bestx4/results_DHTCUN_SRForm2_bestx4.xlsx
+++ b/experiment/SRForm2_bestx4/results_DHTCUN_SRForm2_bestx4.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E221"/>
+  <dimension ref="A1:E411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4035,7 +4035,7 @@
       <c r="D211" t="n">
         <v>0.02551</v>
       </c>
-      <c r="E211" s="3" t="n">
+      <c r="E211" s="2" t="n">
         <v>32.034</v>
       </c>
     </row>
@@ -4207,6 +4207,3236 @@
       </c>
       <c r="E221" t="n">
         <v>32.032</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C222" t="n">
+        <v>0.02609</v>
+      </c>
+      <c r="D222" t="n">
+        <v>0.02609</v>
+      </c>
+      <c r="E222" t="n">
+        <v>31.88</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C223" t="n">
+        <v>0.02583</v>
+      </c>
+      <c r="D223" t="n">
+        <v>0.02583</v>
+      </c>
+      <c r="E223" t="n">
+        <v>31.908</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C224" t="n">
+        <v>0.02587</v>
+      </c>
+      <c r="D224" t="n">
+        <v>0.02587</v>
+      </c>
+      <c r="E224" t="n">
+        <v>31.886</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C225" t="n">
+        <v>0.02621</v>
+      </c>
+      <c r="D225" t="n">
+        <v>0.02621</v>
+      </c>
+      <c r="E225" t="n">
+        <v>31.903</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C226" t="n">
+        <v>0.02605</v>
+      </c>
+      <c r="D226" t="n">
+        <v>0.02605</v>
+      </c>
+      <c r="E226" t="n">
+        <v>31.95</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C227" t="n">
+        <v>0.02577</v>
+      </c>
+      <c r="D227" t="n">
+        <v>0.02577</v>
+      </c>
+      <c r="E227" t="n">
+        <v>31.973</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C228" t="n">
+        <v>0.02617</v>
+      </c>
+      <c r="D228" t="n">
+        <v>0.02617</v>
+      </c>
+      <c r="E228" t="n">
+        <v>31.815</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C229" t="n">
+        <v>0.02615</v>
+      </c>
+      <c r="D229" t="n">
+        <v>0.02615</v>
+      </c>
+      <c r="E229" t="n">
+        <v>31.958</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C230" t="n">
+        <v>0.02627000000000001</v>
+      </c>
+      <c r="D230" t="n">
+        <v>0.02627000000000001</v>
+      </c>
+      <c r="E230" t="n">
+        <v>31.938</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C231" t="n">
+        <v>0.02583</v>
+      </c>
+      <c r="D231" t="n">
+        <v>0.02583</v>
+      </c>
+      <c r="E231" t="n">
+        <v>31.919</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C232" t="n">
+        <v>0.02617000000000001</v>
+      </c>
+      <c r="D232" t="n">
+        <v>0.02617000000000001</v>
+      </c>
+      <c r="E232" t="n">
+        <v>31.913</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C233" t="n">
+        <v>0.02566</v>
+      </c>
+      <c r="D233" t="n">
+        <v>0.02566</v>
+      </c>
+      <c r="E233" t="n">
+        <v>31.924</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C234" t="n">
+        <v>0.02626</v>
+      </c>
+      <c r="D234" t="n">
+        <v>0.02626</v>
+      </c>
+      <c r="E234" t="n">
+        <v>31.86</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C235" t="n">
+        <v>0.02587</v>
+      </c>
+      <c r="D235" t="n">
+        <v>0.02587</v>
+      </c>
+      <c r="E235" t="n">
+        <v>31.925</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C236" t="n">
+        <v>0.02606</v>
+      </c>
+      <c r="D236" t="n">
+        <v>0.02606</v>
+      </c>
+      <c r="E236" t="n">
+        <v>31.957</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C237" t="n">
+        <v>0.0255</v>
+      </c>
+      <c r="D237" t="n">
+        <v>0.0255</v>
+      </c>
+      <c r="E237" t="n">
+        <v>31.981</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C238" t="n">
+        <v>0.02575</v>
+      </c>
+      <c r="D238" t="n">
+        <v>0.02575</v>
+      </c>
+      <c r="E238" t="n">
+        <v>32.009</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C239" t="n">
+        <v>0.02583</v>
+      </c>
+      <c r="D239" t="n">
+        <v>0.02583</v>
+      </c>
+      <c r="E239" t="n">
+        <v>31.938</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C240" t="n">
+        <v>0.02552</v>
+      </c>
+      <c r="D240" t="n">
+        <v>0.02552</v>
+      </c>
+      <c r="E240" t="n">
+        <v>31.97</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C241" t="n">
+        <v>0.0258</v>
+      </c>
+      <c r="D241" t="n">
+        <v>0.0258</v>
+      </c>
+      <c r="E241" t="n">
+        <v>31.95</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C242" t="n">
+        <v>0.02594</v>
+      </c>
+      <c r="D242" t="n">
+        <v>0.02594</v>
+      </c>
+      <c r="E242" t="n">
+        <v>31.967</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>242</v>
+      </c>
+      <c r="B243" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C243" t="n">
+        <v>0.02597</v>
+      </c>
+      <c r="D243" t="n">
+        <v>0.02597</v>
+      </c>
+      <c r="E243" t="n">
+        <v>31.968</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C244" t="n">
+        <v>0.02602</v>
+      </c>
+      <c r="D244" t="n">
+        <v>0.02602</v>
+      </c>
+      <c r="E244" t="n">
+        <v>31.957</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C245" t="n">
+        <v>0.02624</v>
+      </c>
+      <c r="D245" t="n">
+        <v>0.02624</v>
+      </c>
+      <c r="E245" t="n">
+        <v>31.962</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C246" t="n">
+        <v>0.02561</v>
+      </c>
+      <c r="D246" t="n">
+        <v>0.02561</v>
+      </c>
+      <c r="E246" t="n">
+        <v>31.98</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C247" t="n">
+        <v>0.0262</v>
+      </c>
+      <c r="D247" t="n">
+        <v>0.0262</v>
+      </c>
+      <c r="E247" t="n">
+        <v>31.988</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C248" t="n">
+        <v>0.02583</v>
+      </c>
+      <c r="D248" t="n">
+        <v>0.02583</v>
+      </c>
+      <c r="E248" t="n">
+        <v>31.903</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C249" t="n">
+        <v>0.02585</v>
+      </c>
+      <c r="D249" t="n">
+        <v>0.02585</v>
+      </c>
+      <c r="E249" t="n">
+        <v>31.986</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C250" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="D250" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="E250" t="n">
+        <v>31.896</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C251" t="n">
+        <v>0.0259</v>
+      </c>
+      <c r="D251" t="n">
+        <v>0.0259</v>
+      </c>
+      <c r="E251" t="n">
+        <v>31.975</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C252" t="n">
+        <v>0.02601</v>
+      </c>
+      <c r="D252" t="n">
+        <v>0.02601</v>
+      </c>
+      <c r="E252" t="n">
+        <v>31.971</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C253" t="n">
+        <v>0.02609</v>
+      </c>
+      <c r="D253" t="n">
+        <v>0.02609</v>
+      </c>
+      <c r="E253" t="n">
+        <v>31.856</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>253</v>
+      </c>
+      <c r="B254" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C254" t="n">
+        <v>0.02545</v>
+      </c>
+      <c r="D254" t="n">
+        <v>0.02545</v>
+      </c>
+      <c r="E254" t="n">
+        <v>31.987</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C255" t="n">
+        <v>0.02571</v>
+      </c>
+      <c r="D255" t="n">
+        <v>0.02571</v>
+      </c>
+      <c r="E255" t="n">
+        <v>31.94</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>255</v>
+      </c>
+      <c r="B256" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C256" t="n">
+        <v>0.02581</v>
+      </c>
+      <c r="D256" t="n">
+        <v>0.02581</v>
+      </c>
+      <c r="E256" t="n">
+        <v>31.946</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C257" t="n">
+        <v>0.02609</v>
+      </c>
+      <c r="D257" t="n">
+        <v>0.02609</v>
+      </c>
+      <c r="E257" t="n">
+        <v>31.946</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C258" t="n">
+        <v>0.02585</v>
+      </c>
+      <c r="D258" t="n">
+        <v>0.02585</v>
+      </c>
+      <c r="E258" t="n">
+        <v>31.998</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C259" t="n">
+        <v>0.02556</v>
+      </c>
+      <c r="D259" t="n">
+        <v>0.02556</v>
+      </c>
+      <c r="E259" t="n">
+        <v>31.974</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C260" t="n">
+        <v>0.02595</v>
+      </c>
+      <c r="D260" t="n">
+        <v>0.02595</v>
+      </c>
+      <c r="E260" t="n">
+        <v>31.97</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C261" t="n">
+        <v>0.02573</v>
+      </c>
+      <c r="D261" t="n">
+        <v>0.02573</v>
+      </c>
+      <c r="E261" t="n">
+        <v>31.902</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C262" t="n">
+        <v>0.02564</v>
+      </c>
+      <c r="D262" t="n">
+        <v>0.02564</v>
+      </c>
+      <c r="E262" t="n">
+        <v>31.994</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>262</v>
+      </c>
+      <c r="B263" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C263" t="n">
+        <v>0.02619</v>
+      </c>
+      <c r="D263" t="n">
+        <v>0.02619</v>
+      </c>
+      <c r="E263" t="n">
+        <v>32.012</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>263</v>
+      </c>
+      <c r="B264" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C264" t="n">
+        <v>0.02568</v>
+      </c>
+      <c r="D264" t="n">
+        <v>0.02568</v>
+      </c>
+      <c r="E264" t="n">
+        <v>31.935</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>264</v>
+      </c>
+      <c r="B265" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C265" t="n">
+        <v>0.0261</v>
+      </c>
+      <c r="D265" t="n">
+        <v>0.0261</v>
+      </c>
+      <c r="E265" t="n">
+        <v>31.955</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>265</v>
+      </c>
+      <c r="B266" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C266" t="n">
+        <v>0.02614</v>
+      </c>
+      <c r="D266" t="n">
+        <v>0.02614</v>
+      </c>
+      <c r="E266" t="n">
+        <v>32.004</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>266</v>
+      </c>
+      <c r="B267" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C267" t="n">
+        <v>0.02603</v>
+      </c>
+      <c r="D267" t="n">
+        <v>0.02603</v>
+      </c>
+      <c r="E267" t="n">
+        <v>31.922</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>267</v>
+      </c>
+      <c r="B268" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C268" t="n">
+        <v>0.02576</v>
+      </c>
+      <c r="D268" t="n">
+        <v>0.02576</v>
+      </c>
+      <c r="E268" t="n">
+        <v>31.96</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>268</v>
+      </c>
+      <c r="B269" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C269" t="n">
+        <v>0.02572</v>
+      </c>
+      <c r="D269" t="n">
+        <v>0.02572</v>
+      </c>
+      <c r="E269" t="n">
+        <v>31.997</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>269</v>
+      </c>
+      <c r="B270" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C270" t="n">
+        <v>0.02561</v>
+      </c>
+      <c r="D270" t="n">
+        <v>0.02561</v>
+      </c>
+      <c r="E270" t="n">
+        <v>31.982</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>270</v>
+      </c>
+      <c r="B271" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C271" t="n">
+        <v>0.02566</v>
+      </c>
+      <c r="D271" t="n">
+        <v>0.02566</v>
+      </c>
+      <c r="E271" t="n">
+        <v>31.989</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>271</v>
+      </c>
+      <c r="B272" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C272" t="n">
+        <v>0.02604</v>
+      </c>
+      <c r="D272" t="n">
+        <v>0.02604</v>
+      </c>
+      <c r="E272" t="n">
+        <v>31.971</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>272</v>
+      </c>
+      <c r="B273" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C273" t="n">
+        <v>0.0254</v>
+      </c>
+      <c r="D273" t="n">
+        <v>0.0254</v>
+      </c>
+      <c r="E273" t="n">
+        <v>32.019</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>273</v>
+      </c>
+      <c r="B274" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C274" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="D274" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="E274" t="n">
+        <v>31.987</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>274</v>
+      </c>
+      <c r="B275" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C275" t="n">
+        <v>0.02576</v>
+      </c>
+      <c r="D275" t="n">
+        <v>0.02576</v>
+      </c>
+      <c r="E275" t="n">
+        <v>32.009</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>275</v>
+      </c>
+      <c r="B276" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C276" t="n">
+        <v>0.02575</v>
+      </c>
+      <c r="D276" t="n">
+        <v>0.02575</v>
+      </c>
+      <c r="E276" t="n">
+        <v>32.003</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>276</v>
+      </c>
+      <c r="B277" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C277" t="n">
+        <v>0.0256</v>
+      </c>
+      <c r="D277" t="n">
+        <v>0.0256</v>
+      </c>
+      <c r="E277" t="n">
+        <v>31.992</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>277</v>
+      </c>
+      <c r="B278" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C278" t="n">
+        <v>0.02615</v>
+      </c>
+      <c r="D278" t="n">
+        <v>0.02615</v>
+      </c>
+      <c r="E278" s="2" t="n">
+        <v>32.046</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>278</v>
+      </c>
+      <c r="B279" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C279" t="n">
+        <v>0.02564</v>
+      </c>
+      <c r="D279" t="n">
+        <v>0.02564</v>
+      </c>
+      <c r="E279" t="n">
+        <v>32.008</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>279</v>
+      </c>
+      <c r="B280" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C280" t="n">
+        <v>0.02607</v>
+      </c>
+      <c r="D280" t="n">
+        <v>0.02607</v>
+      </c>
+      <c r="E280" s="2" t="n">
+        <v>32.049</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>280</v>
+      </c>
+      <c r="B281" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C281" t="n">
+        <v>0.02645</v>
+      </c>
+      <c r="D281" t="n">
+        <v>0.02645</v>
+      </c>
+      <c r="E281" t="n">
+        <v>32.007</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>281</v>
+      </c>
+      <c r="B282" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C282" t="n">
+        <v>0.02573</v>
+      </c>
+      <c r="D282" t="n">
+        <v>0.02573</v>
+      </c>
+      <c r="E282" t="n">
+        <v>31.99</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>282</v>
+      </c>
+      <c r="B283" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C283" t="n">
+        <v>0.02552</v>
+      </c>
+      <c r="D283" t="n">
+        <v>0.02552</v>
+      </c>
+      <c r="E283" t="n">
+        <v>31.926</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>283</v>
+      </c>
+      <c r="B284" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C284" t="n">
+        <v>0.02598</v>
+      </c>
+      <c r="D284" t="n">
+        <v>0.02598</v>
+      </c>
+      <c r="E284" t="n">
+        <v>31.983</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>284</v>
+      </c>
+      <c r="B285" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C285" t="n">
+        <v>0.02602</v>
+      </c>
+      <c r="D285" t="n">
+        <v>0.02602</v>
+      </c>
+      <c r="E285" t="n">
+        <v>31.976</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>285</v>
+      </c>
+      <c r="B286" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C286" t="n">
+        <v>0.02597</v>
+      </c>
+      <c r="D286" t="n">
+        <v>0.02597</v>
+      </c>
+      <c r="E286" t="n">
+        <v>32.046</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>286</v>
+      </c>
+      <c r="B287" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C287" t="n">
+        <v>0.02535</v>
+      </c>
+      <c r="D287" t="n">
+        <v>0.02535</v>
+      </c>
+      <c r="E287" t="n">
+        <v>32.008</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>287</v>
+      </c>
+      <c r="B288" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C288" t="n">
+        <v>0.02584</v>
+      </c>
+      <c r="D288" t="n">
+        <v>0.02584</v>
+      </c>
+      <c r="E288" t="n">
+        <v>32.041</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>288</v>
+      </c>
+      <c r="B289" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C289" t="n">
+        <v>0.02564</v>
+      </c>
+      <c r="D289" t="n">
+        <v>0.02564</v>
+      </c>
+      <c r="E289" t="n">
+        <v>31.979</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>289</v>
+      </c>
+      <c r="B290" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C290" t="n">
+        <v>0.0257</v>
+      </c>
+      <c r="D290" t="n">
+        <v>0.0257</v>
+      </c>
+      <c r="E290" s="2" t="n">
+        <v>32.072</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>290</v>
+      </c>
+      <c r="B291" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C291" t="n">
+        <v>0.02574</v>
+      </c>
+      <c r="D291" t="n">
+        <v>0.02574</v>
+      </c>
+      <c r="E291" t="n">
+        <v>32.014</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>291</v>
+      </c>
+      <c r="B292" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C292" t="n">
+        <v>0.0259</v>
+      </c>
+      <c r="D292" t="n">
+        <v>0.0259</v>
+      </c>
+      <c r="E292" t="n">
+        <v>32.017</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>292</v>
+      </c>
+      <c r="B293" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C293" t="n">
+        <v>0.02576</v>
+      </c>
+      <c r="D293" t="n">
+        <v>0.02576</v>
+      </c>
+      <c r="E293" t="n">
+        <v>32.053</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>293</v>
+      </c>
+      <c r="B294" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C294" t="n">
+        <v>0.02579</v>
+      </c>
+      <c r="D294" t="n">
+        <v>0.02579</v>
+      </c>
+      <c r="E294" t="n">
+        <v>32.039</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>294</v>
+      </c>
+      <c r="B295" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C295" t="n">
+        <v>0.02531</v>
+      </c>
+      <c r="D295" t="n">
+        <v>0.02531</v>
+      </c>
+      <c r="E295" t="n">
+        <v>31.976</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>295</v>
+      </c>
+      <c r="B296" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C296" t="n">
+        <v>0.02578</v>
+      </c>
+      <c r="D296" t="n">
+        <v>0.02578</v>
+      </c>
+      <c r="E296" t="n">
+        <v>31.917</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>296</v>
+      </c>
+      <c r="B297" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C297" t="n">
+        <v>0.02558</v>
+      </c>
+      <c r="D297" t="n">
+        <v>0.02558</v>
+      </c>
+      <c r="E297" t="n">
+        <v>32.036</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>297</v>
+      </c>
+      <c r="B298" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C298" t="n">
+        <v>0.02541000000000001</v>
+      </c>
+      <c r="D298" t="n">
+        <v>0.02541000000000001</v>
+      </c>
+      <c r="E298" t="n">
+        <v>32.027</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>298</v>
+      </c>
+      <c r="B299" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C299" t="n">
+        <v>0.02583</v>
+      </c>
+      <c r="D299" t="n">
+        <v>0.02583</v>
+      </c>
+      <c r="E299" s="2" t="n">
+        <v>32.081</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>299</v>
+      </c>
+      <c r="B300" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C300" t="n">
+        <v>0.02534</v>
+      </c>
+      <c r="D300" t="n">
+        <v>0.02534</v>
+      </c>
+      <c r="E300" t="n">
+        <v>32.005</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>300</v>
+      </c>
+      <c r="B301" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C301" t="n">
+        <v>0.02572</v>
+      </c>
+      <c r="D301" t="n">
+        <v>0.02572</v>
+      </c>
+      <c r="E301" t="n">
+        <v>32.035</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>301</v>
+      </c>
+      <c r="B302" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C302" t="n">
+        <v>0.02548</v>
+      </c>
+      <c r="D302" t="n">
+        <v>0.02548</v>
+      </c>
+      <c r="E302" t="n">
+        <v>32.012</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>302</v>
+      </c>
+      <c r="B303" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C303" t="n">
+        <v>0.02589</v>
+      </c>
+      <c r="D303" t="n">
+        <v>0.02589</v>
+      </c>
+      <c r="E303" t="n">
+        <v>32.005</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>303</v>
+      </c>
+      <c r="B304" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C304" t="n">
+        <v>0.02542</v>
+      </c>
+      <c r="D304" t="n">
+        <v>0.02542</v>
+      </c>
+      <c r="E304" t="n">
+        <v>32.059</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>304</v>
+      </c>
+      <c r="B305" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C305" t="n">
+        <v>0.02576</v>
+      </c>
+      <c r="D305" t="n">
+        <v>0.02576</v>
+      </c>
+      <c r="E305" t="n">
+        <v>32.04</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>305</v>
+      </c>
+      <c r="B306" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C306" t="n">
+        <v>0.02568</v>
+      </c>
+      <c r="D306" t="n">
+        <v>0.02568</v>
+      </c>
+      <c r="E306" t="n">
+        <v>32.071</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>306</v>
+      </c>
+      <c r="B307" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C307" t="n">
+        <v>0.02591</v>
+      </c>
+      <c r="D307" t="n">
+        <v>0.02591</v>
+      </c>
+      <c r="E307" t="n">
+        <v>32.062</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>307</v>
+      </c>
+      <c r="B308" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C308" t="n">
+        <v>0.02556</v>
+      </c>
+      <c r="D308" t="n">
+        <v>0.02556</v>
+      </c>
+      <c r="E308" t="n">
+        <v>32.021</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>308</v>
+      </c>
+      <c r="B309" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C309" t="n">
+        <v>0.02564</v>
+      </c>
+      <c r="D309" t="n">
+        <v>0.02564</v>
+      </c>
+      <c r="E309" t="n">
+        <v>31.973</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>309</v>
+      </c>
+      <c r="B310" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C310" t="n">
+        <v>0.02599</v>
+      </c>
+      <c r="D310" t="n">
+        <v>0.02599</v>
+      </c>
+      <c r="E310" s="2" t="n">
+        <v>32.087</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>310</v>
+      </c>
+      <c r="B311" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C311" t="n">
+        <v>0.02578</v>
+      </c>
+      <c r="D311" t="n">
+        <v>0.02578</v>
+      </c>
+      <c r="E311" t="n">
+        <v>32.082</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>311</v>
+      </c>
+      <c r="B312" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C312" t="n">
+        <v>0.02576</v>
+      </c>
+      <c r="D312" t="n">
+        <v>0.02576</v>
+      </c>
+      <c r="E312" t="n">
+        <v>32.014</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>312</v>
+      </c>
+      <c r="B313" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C313" t="n">
+        <v>0.02545</v>
+      </c>
+      <c r="D313" t="n">
+        <v>0.02545</v>
+      </c>
+      <c r="E313" t="n">
+        <v>32.036</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>313</v>
+      </c>
+      <c r="B314" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C314" t="n">
+        <v>0.02561</v>
+      </c>
+      <c r="D314" t="n">
+        <v>0.02561</v>
+      </c>
+      <c r="E314" t="n">
+        <v>32.045</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>314</v>
+      </c>
+      <c r="B315" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C315" t="n">
+        <v>0.02524</v>
+      </c>
+      <c r="D315" t="n">
+        <v>0.02524</v>
+      </c>
+      <c r="E315" t="n">
+        <v>32.059</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>315</v>
+      </c>
+      <c r="B316" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C316" t="n">
+        <v>0.02584</v>
+      </c>
+      <c r="D316" t="n">
+        <v>0.02584</v>
+      </c>
+      <c r="E316" t="n">
+        <v>32.072</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>316</v>
+      </c>
+      <c r="B317" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C317" t="n">
+        <v>0.02555</v>
+      </c>
+      <c r="D317" t="n">
+        <v>0.02555</v>
+      </c>
+      <c r="E317" t="n">
+        <v>32.066</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>317</v>
+      </c>
+      <c r="B318" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C318" t="n">
+        <v>0.02564</v>
+      </c>
+      <c r="D318" t="n">
+        <v>0.02564</v>
+      </c>
+      <c r="E318" t="n">
+        <v>32.077</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>318</v>
+      </c>
+      <c r="B319" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C319" t="n">
+        <v>0.02609</v>
+      </c>
+      <c r="D319" t="n">
+        <v>0.02609</v>
+      </c>
+      <c r="E319" t="n">
+        <v>32.075</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>319</v>
+      </c>
+      <c r="B320" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C320" t="n">
+        <v>0.02552</v>
+      </c>
+      <c r="D320" t="n">
+        <v>0.02552</v>
+      </c>
+      <c r="E320" t="n">
+        <v>32.032</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>320</v>
+      </c>
+      <c r="B321" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C321" t="n">
+        <v>0.02601</v>
+      </c>
+      <c r="D321" t="n">
+        <v>0.02601</v>
+      </c>
+      <c r="E321" t="n">
+        <v>32.043</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>321</v>
+      </c>
+      <c r="B322" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C322" t="n">
+        <v>0.02555</v>
+      </c>
+      <c r="D322" t="n">
+        <v>0.02555</v>
+      </c>
+      <c r="E322" t="n">
+        <v>32.051</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>322</v>
+      </c>
+      <c r="B323" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C323" t="n">
+        <v>0.02583</v>
+      </c>
+      <c r="D323" t="n">
+        <v>0.02583</v>
+      </c>
+      <c r="E323" t="n">
+        <v>32.075</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>323</v>
+      </c>
+      <c r="B324" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C324" t="n">
+        <v>0.02554</v>
+      </c>
+      <c r="D324" t="n">
+        <v>0.02554</v>
+      </c>
+      <c r="E324" t="n">
+        <v>32.056</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>324</v>
+      </c>
+      <c r="B325" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C325" t="n">
+        <v>0.02528</v>
+      </c>
+      <c r="D325" t="n">
+        <v>0.02528</v>
+      </c>
+      <c r="E325" s="2" t="n">
+        <v>32.091</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>325</v>
+      </c>
+      <c r="B326" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C326" t="n">
+        <v>0.0255</v>
+      </c>
+      <c r="D326" t="n">
+        <v>0.0255</v>
+      </c>
+      <c r="E326" s="2" t="n">
+        <v>32.107</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>326</v>
+      </c>
+      <c r="B327" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C327" t="n">
+        <v>0.02596</v>
+      </c>
+      <c r="D327" t="n">
+        <v>0.02596</v>
+      </c>
+      <c r="E327" t="n">
+        <v>32.047</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>327</v>
+      </c>
+      <c r="B328" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C328" t="n">
+        <v>0.02589</v>
+      </c>
+      <c r="D328" t="n">
+        <v>0.02589</v>
+      </c>
+      <c r="E328" t="n">
+        <v>32.081</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>328</v>
+      </c>
+      <c r="B329" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C329" t="n">
+        <v>0.02565</v>
+      </c>
+      <c r="D329" t="n">
+        <v>0.02565</v>
+      </c>
+      <c r="E329" t="n">
+        <v>32.079</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>329</v>
+      </c>
+      <c r="B330" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C330" t="n">
+        <v>0.02598</v>
+      </c>
+      <c r="D330" t="n">
+        <v>0.02598</v>
+      </c>
+      <c r="E330" t="n">
+        <v>32.036</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>330</v>
+      </c>
+      <c r="B331" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C331" t="n">
+        <v>0.02541</v>
+      </c>
+      <c r="D331" t="n">
+        <v>0.02541</v>
+      </c>
+      <c r="E331" t="n">
+        <v>32.069</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>331</v>
+      </c>
+      <c r="B332" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C332" t="n">
+        <v>0.02563</v>
+      </c>
+      <c r="D332" t="n">
+        <v>0.02563</v>
+      </c>
+      <c r="E332" t="n">
+        <v>31.995</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>332</v>
+      </c>
+      <c r="B333" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C333" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="D333" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="E333" t="n">
+        <v>32.054</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>333</v>
+      </c>
+      <c r="B334" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C334" t="n">
+        <v>0.0259</v>
+      </c>
+      <c r="D334" t="n">
+        <v>0.0259</v>
+      </c>
+      <c r="E334" t="n">
+        <v>32.087</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>334</v>
+      </c>
+      <c r="B335" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C335" t="n">
+        <v>0.02574</v>
+      </c>
+      <c r="D335" t="n">
+        <v>0.02574</v>
+      </c>
+      <c r="E335" t="n">
+        <v>32.041</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>335</v>
+      </c>
+      <c r="B336" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C336" t="n">
+        <v>0.0258</v>
+      </c>
+      <c r="D336" t="n">
+        <v>0.0258</v>
+      </c>
+      <c r="E336" t="n">
+        <v>32.086</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>336</v>
+      </c>
+      <c r="B337" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C337" t="n">
+        <v>0.02548</v>
+      </c>
+      <c r="D337" t="n">
+        <v>0.02548</v>
+      </c>
+      <c r="E337" t="n">
+        <v>32.088</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>337</v>
+      </c>
+      <c r="B338" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C338" t="n">
+        <v>0.02586</v>
+      </c>
+      <c r="D338" t="n">
+        <v>0.02586</v>
+      </c>
+      <c r="E338" t="n">
+        <v>32.059</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>338</v>
+      </c>
+      <c r="B339" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C339" t="n">
+        <v>0.02561</v>
+      </c>
+      <c r="D339" t="n">
+        <v>0.02561</v>
+      </c>
+      <c r="E339" t="n">
+        <v>32.08</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>339</v>
+      </c>
+      <c r="B340" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C340" t="n">
+        <v>0.02606</v>
+      </c>
+      <c r="D340" t="n">
+        <v>0.02606</v>
+      </c>
+      <c r="E340" t="n">
+        <v>32.085</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>340</v>
+      </c>
+      <c r="B341" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C341" t="n">
+        <v>0.02587</v>
+      </c>
+      <c r="D341" t="n">
+        <v>0.02587</v>
+      </c>
+      <c r="E341" t="n">
+        <v>32.1</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>341</v>
+      </c>
+      <c r="B342" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C342" t="n">
+        <v>0.02578</v>
+      </c>
+      <c r="D342" t="n">
+        <v>0.02578</v>
+      </c>
+      <c r="E342" t="n">
+        <v>32.073</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>342</v>
+      </c>
+      <c r="B343" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C343" t="n">
+        <v>0.02525</v>
+      </c>
+      <c r="D343" t="n">
+        <v>0.02525</v>
+      </c>
+      <c r="E343" t="n">
+        <v>31.981</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>343</v>
+      </c>
+      <c r="B344" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C344" t="n">
+        <v>0.0259</v>
+      </c>
+      <c r="D344" t="n">
+        <v>0.0259</v>
+      </c>
+      <c r="E344" t="n">
+        <v>32.062</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>344</v>
+      </c>
+      <c r="B345" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C345" t="n">
+        <v>0.0259</v>
+      </c>
+      <c r="D345" t="n">
+        <v>0.0259</v>
+      </c>
+      <c r="E345" t="n">
+        <v>32.002</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>345</v>
+      </c>
+      <c r="B346" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C346" t="n">
+        <v>0.02582</v>
+      </c>
+      <c r="D346" t="n">
+        <v>0.02582</v>
+      </c>
+      <c r="E346" t="n">
+        <v>32.09</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>346</v>
+      </c>
+      <c r="B347" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C347" t="n">
+        <v>0.02588</v>
+      </c>
+      <c r="D347" t="n">
+        <v>0.02588</v>
+      </c>
+      <c r="E347" t="n">
+        <v>31.944</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>347</v>
+      </c>
+      <c r="B348" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C348" t="n">
+        <v>0.02579</v>
+      </c>
+      <c r="D348" t="n">
+        <v>0.02579</v>
+      </c>
+      <c r="E348" t="n">
+        <v>32.1</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>348</v>
+      </c>
+      <c r="B349" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C349" t="n">
+        <v>0.02539</v>
+      </c>
+      <c r="D349" t="n">
+        <v>0.02539</v>
+      </c>
+      <c r="E349" t="n">
+        <v>32.089</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>349</v>
+      </c>
+      <c r="B350" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C350" t="n">
+        <v>0.02571</v>
+      </c>
+      <c r="D350" t="n">
+        <v>0.02571</v>
+      </c>
+      <c r="E350" t="n">
+        <v>32.053</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>350</v>
+      </c>
+      <c r="B351" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C351" t="n">
+        <v>0.02561</v>
+      </c>
+      <c r="D351" t="n">
+        <v>0.02561</v>
+      </c>
+      <c r="E351" s="2" t="n">
+        <v>32.121</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>351</v>
+      </c>
+      <c r="B352" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C352" t="n">
+        <v>0.02534</v>
+      </c>
+      <c r="D352" t="n">
+        <v>0.02534</v>
+      </c>
+      <c r="E352" t="n">
+        <v>32.085</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>352</v>
+      </c>
+      <c r="B353" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C353" t="n">
+        <v>0.02546</v>
+      </c>
+      <c r="D353" t="n">
+        <v>0.02546</v>
+      </c>
+      <c r="E353" t="n">
+        <v>32.084</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>353</v>
+      </c>
+      <c r="B354" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C354" t="n">
+        <v>0.02578</v>
+      </c>
+      <c r="D354" t="n">
+        <v>0.02578</v>
+      </c>
+      <c r="E354" t="n">
+        <v>32.105</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>354</v>
+      </c>
+      <c r="B355" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C355" t="n">
+        <v>0.02592</v>
+      </c>
+      <c r="D355" t="n">
+        <v>0.02592</v>
+      </c>
+      <c r="E355" t="n">
+        <v>32.097</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>355</v>
+      </c>
+      <c r="B356" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C356" t="n">
+        <v>0.02616</v>
+      </c>
+      <c r="D356" t="n">
+        <v>0.02616</v>
+      </c>
+      <c r="E356" t="n">
+        <v>31.991</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>356</v>
+      </c>
+      <c r="B357" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C357" t="n">
+        <v>0.02552</v>
+      </c>
+      <c r="D357" t="n">
+        <v>0.02552</v>
+      </c>
+      <c r="E357" t="n">
+        <v>32.088</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>357</v>
+      </c>
+      <c r="B358" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C358" t="n">
+        <v>0.02607</v>
+      </c>
+      <c r="D358" t="n">
+        <v>0.02607</v>
+      </c>
+      <c r="E358" t="n">
+        <v>32.098</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>358</v>
+      </c>
+      <c r="B359" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C359" t="n">
+        <v>0.02539</v>
+      </c>
+      <c r="D359" t="n">
+        <v>0.02539</v>
+      </c>
+      <c r="E359" s="2" t="n">
+        <v>32.124</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>359</v>
+      </c>
+      <c r="B360" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C360" t="n">
+        <v>0.02579</v>
+      </c>
+      <c r="D360" t="n">
+        <v>0.02579</v>
+      </c>
+      <c r="E360" t="n">
+        <v>32.051</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>360</v>
+      </c>
+      <c r="B361" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C361" t="n">
+        <v>0.02576</v>
+      </c>
+      <c r="D361" t="n">
+        <v>0.02576</v>
+      </c>
+      <c r="E361" t="n">
+        <v>32.037</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>361</v>
+      </c>
+      <c r="B362" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C362" t="n">
+        <v>0.02562</v>
+      </c>
+      <c r="D362" t="n">
+        <v>0.02562</v>
+      </c>
+      <c r="E362" t="n">
+        <v>32.104</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>362</v>
+      </c>
+      <c r="B363" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C363" t="n">
+        <v>0.02572</v>
+      </c>
+      <c r="D363" t="n">
+        <v>0.02572</v>
+      </c>
+      <c r="E363" t="n">
+        <v>32.069</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>363</v>
+      </c>
+      <c r="B364" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C364" t="n">
+        <v>0.02566</v>
+      </c>
+      <c r="D364" t="n">
+        <v>0.02566</v>
+      </c>
+      <c r="E364" t="n">
+        <v>32.105</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>364</v>
+      </c>
+      <c r="B365" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C365" t="n">
+        <v>0.02533</v>
+      </c>
+      <c r="D365" t="n">
+        <v>0.02533</v>
+      </c>
+      <c r="E365" t="n">
+        <v>32.037</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>365</v>
+      </c>
+      <c r="B366" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C366" t="n">
+        <v>0.02558</v>
+      </c>
+      <c r="D366" t="n">
+        <v>0.02558</v>
+      </c>
+      <c r="E366" t="n">
+        <v>32.109</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>366</v>
+      </c>
+      <c r="B367" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C367" t="n">
+        <v>0.02579</v>
+      </c>
+      <c r="D367" t="n">
+        <v>0.02579</v>
+      </c>
+      <c r="E367" t="n">
+        <v>32.123</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>367</v>
+      </c>
+      <c r="B368" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C368" t="n">
+        <v>0.02578</v>
+      </c>
+      <c r="D368" t="n">
+        <v>0.02578</v>
+      </c>
+      <c r="E368" t="n">
+        <v>32.074</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>368</v>
+      </c>
+      <c r="B369" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C369" t="n">
+        <v>0.02512</v>
+      </c>
+      <c r="D369" t="n">
+        <v>0.02512</v>
+      </c>
+      <c r="E369" t="n">
+        <v>32.106</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>369</v>
+      </c>
+      <c r="B370" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C370" t="n">
+        <v>0.02562</v>
+      </c>
+      <c r="D370" t="n">
+        <v>0.02562</v>
+      </c>
+      <c r="E370" t="n">
+        <v>32.088</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>370</v>
+      </c>
+      <c r="B371" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C371" t="n">
+        <v>0.02562</v>
+      </c>
+      <c r="D371" t="n">
+        <v>0.02562</v>
+      </c>
+      <c r="E371" t="n">
+        <v>32.039</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>371</v>
+      </c>
+      <c r="B372" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C372" t="n">
+        <v>0.02611</v>
+      </c>
+      <c r="D372" t="n">
+        <v>0.02611</v>
+      </c>
+      <c r="E372" t="n">
+        <v>32.093</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>372</v>
+      </c>
+      <c r="B373" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C373" t="n">
+        <v>0.02544</v>
+      </c>
+      <c r="D373" t="n">
+        <v>0.02544</v>
+      </c>
+      <c r="E373" t="n">
+        <v>32.077</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>373</v>
+      </c>
+      <c r="B374" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C374" t="n">
+        <v>0.02598</v>
+      </c>
+      <c r="D374" t="n">
+        <v>0.02598</v>
+      </c>
+      <c r="E374" t="n">
+        <v>32.121</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>374</v>
+      </c>
+      <c r="B375" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C375" t="n">
+        <v>0.02558</v>
+      </c>
+      <c r="D375" t="n">
+        <v>0.02558</v>
+      </c>
+      <c r="E375" t="n">
+        <v>32.075</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>375</v>
+      </c>
+      <c r="B376" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C376" t="n">
+        <v>0.02567000000000001</v>
+      </c>
+      <c r="D376" t="n">
+        <v>0.02567000000000001</v>
+      </c>
+      <c r="E376" t="n">
+        <v>32.062</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>376</v>
+      </c>
+      <c r="B377" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C377" t="n">
+        <v>0.02555</v>
+      </c>
+      <c r="D377" t="n">
+        <v>0.02555</v>
+      </c>
+      <c r="E377" t="n">
+        <v>32.098</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>377</v>
+      </c>
+      <c r="B378" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C378" t="n">
+        <v>0.02529</v>
+      </c>
+      <c r="D378" t="n">
+        <v>0.02529</v>
+      </c>
+      <c r="E378" t="n">
+        <v>32.119</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>378</v>
+      </c>
+      <c r="B379" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C379" t="n">
+        <v>0.02564</v>
+      </c>
+      <c r="D379" t="n">
+        <v>0.02564</v>
+      </c>
+      <c r="E379" t="n">
+        <v>32.039</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>379</v>
+      </c>
+      <c r="B380" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C380" t="n">
+        <v>0.02589</v>
+      </c>
+      <c r="D380" t="n">
+        <v>0.02589</v>
+      </c>
+      <c r="E380" t="n">
+        <v>32.033</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>380</v>
+      </c>
+      <c r="B381" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C381" t="n">
+        <v>0.02534</v>
+      </c>
+      <c r="D381" t="n">
+        <v>0.02534</v>
+      </c>
+      <c r="E381" s="2" t="n">
+        <v>32.14</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>381</v>
+      </c>
+      <c r="B382" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C382" t="n">
+        <v>0.0255</v>
+      </c>
+      <c r="D382" t="n">
+        <v>0.0255</v>
+      </c>
+      <c r="E382" t="n">
+        <v>31.847</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>382</v>
+      </c>
+      <c r="B383" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C383" t="n">
+        <v>0.02552</v>
+      </c>
+      <c r="D383" t="n">
+        <v>0.02552</v>
+      </c>
+      <c r="E383" t="n">
+        <v>32.121</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>383</v>
+      </c>
+      <c r="B384" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C384" t="n">
+        <v>0.02564</v>
+      </c>
+      <c r="D384" t="n">
+        <v>0.02564</v>
+      </c>
+      <c r="E384" t="n">
+        <v>32.064</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>384</v>
+      </c>
+      <c r="B385" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C385" t="n">
+        <v>0.02556</v>
+      </c>
+      <c r="D385" t="n">
+        <v>0.02556</v>
+      </c>
+      <c r="E385" t="n">
+        <v>32.117</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>385</v>
+      </c>
+      <c r="B386" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C386" t="n">
+        <v>0.02554</v>
+      </c>
+      <c r="D386" t="n">
+        <v>0.02554</v>
+      </c>
+      <c r="E386" t="n">
+        <v>32.1</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>386</v>
+      </c>
+      <c r="B387" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C387" t="n">
+        <v>0.02556000000000001</v>
+      </c>
+      <c r="D387" t="n">
+        <v>0.02556000000000001</v>
+      </c>
+      <c r="E387" t="n">
+        <v>32.121</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>387</v>
+      </c>
+      <c r="B388" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C388" t="n">
+        <v>0.02567</v>
+      </c>
+      <c r="D388" t="n">
+        <v>0.02567</v>
+      </c>
+      <c r="E388" s="2" t="n">
+        <v>32.149</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>388</v>
+      </c>
+      <c r="B389" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C389" t="n">
+        <v>0.02591</v>
+      </c>
+      <c r="D389" t="n">
+        <v>0.02591</v>
+      </c>
+      <c r="E389" t="n">
+        <v>32.082</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>389</v>
+      </c>
+      <c r="B390" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C390" t="n">
+        <v>0.02533</v>
+      </c>
+      <c r="D390" t="n">
+        <v>0.02533</v>
+      </c>
+      <c r="E390" t="n">
+        <v>32.14</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>390</v>
+      </c>
+      <c r="B391" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C391" t="n">
+        <v>0.02549</v>
+      </c>
+      <c r="D391" t="n">
+        <v>0.02549</v>
+      </c>
+      <c r="E391" t="n">
+        <v>32.104</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>391</v>
+      </c>
+      <c r="B392" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C392" t="n">
+        <v>0.02539</v>
+      </c>
+      <c r="D392" t="n">
+        <v>0.02539</v>
+      </c>
+      <c r="E392" t="n">
+        <v>32.112</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>392</v>
+      </c>
+      <c r="B393" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C393" t="n">
+        <v>0.02532</v>
+      </c>
+      <c r="D393" t="n">
+        <v>0.02532</v>
+      </c>
+      <c r="E393" s="3" t="n">
+        <v>32.157</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>393</v>
+      </c>
+      <c r="B394" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C394" t="n">
+        <v>0.02551</v>
+      </c>
+      <c r="D394" t="n">
+        <v>0.02551</v>
+      </c>
+      <c r="E394" t="n">
+        <v>32.117</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>394</v>
+      </c>
+      <c r="B395" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C395" t="n">
+        <v>0.02511</v>
+      </c>
+      <c r="D395" t="n">
+        <v>0.02511</v>
+      </c>
+      <c r="E395" t="n">
+        <v>31.769</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>395</v>
+      </c>
+      <c r="B396" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C396" t="n">
+        <v>0.02541</v>
+      </c>
+      <c r="D396" t="n">
+        <v>0.02541</v>
+      </c>
+      <c r="E396" t="n">
+        <v>32.115</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>396</v>
+      </c>
+      <c r="B397" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C397" t="n">
+        <v>0.02529</v>
+      </c>
+      <c r="D397" t="n">
+        <v>0.02529</v>
+      </c>
+      <c r="E397" t="n">
+        <v>32.136</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>397</v>
+      </c>
+      <c r="B398" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C398" t="n">
+        <v>0.02599</v>
+      </c>
+      <c r="D398" t="n">
+        <v>0.02599</v>
+      </c>
+      <c r="E398" t="n">
+        <v>32.04</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>398</v>
+      </c>
+      <c r="B399" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C399" t="n">
+        <v>0.02527</v>
+      </c>
+      <c r="D399" t="n">
+        <v>0.02527</v>
+      </c>
+      <c r="E399" t="n">
+        <v>32.106</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>399</v>
+      </c>
+      <c r="B400" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C400" t="n">
+        <v>0.02557</v>
+      </c>
+      <c r="D400" t="n">
+        <v>0.02557</v>
+      </c>
+      <c r="E400" t="n">
+        <v>32.059</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>400</v>
+      </c>
+      <c r="B401" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C401" t="n">
+        <v>0.02532</v>
+      </c>
+      <c r="D401" t="n">
+        <v>0.02532</v>
+      </c>
+      <c r="E401" t="n">
+        <v>32.09</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>401</v>
+      </c>
+      <c r="B402" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C402" t="n">
+        <v>0.02562</v>
+      </c>
+      <c r="D402" t="n">
+        <v>0.02562</v>
+      </c>
+      <c r="E402" t="n">
+        <v>32.139</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>402</v>
+      </c>
+      <c r="B403" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C403" t="n">
+        <v>0.02522</v>
+      </c>
+      <c r="D403" t="n">
+        <v>0.02522</v>
+      </c>
+      <c r="E403" t="n">
+        <v>32.14</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>403</v>
+      </c>
+      <c r="B404" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C404" t="n">
+        <v>0.02546</v>
+      </c>
+      <c r="D404" t="n">
+        <v>0.02546</v>
+      </c>
+      <c r="E404" t="n">
+        <v>32.12</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>404</v>
+      </c>
+      <c r="B405" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C405" t="n">
+        <v>0.02558</v>
+      </c>
+      <c r="D405" t="n">
+        <v>0.02558</v>
+      </c>
+      <c r="E405" t="n">
+        <v>32.131</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>405</v>
+      </c>
+      <c r="B406" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C406" t="n">
+        <v>0.02503</v>
+      </c>
+      <c r="D406" t="n">
+        <v>0.02503</v>
+      </c>
+      <c r="E406" t="n">
+        <v>32.079</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>406</v>
+      </c>
+      <c r="B407" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C407" t="n">
+        <v>0.02564</v>
+      </c>
+      <c r="D407" t="n">
+        <v>0.02564</v>
+      </c>
+      <c r="E407" t="n">
+        <v>32.108</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>407</v>
+      </c>
+      <c r="B408" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C408" t="n">
+        <v>0.02556000000000001</v>
+      </c>
+      <c r="D408" t="n">
+        <v>0.02556000000000001</v>
+      </c>
+      <c r="E408" t="n">
+        <v>32.046</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>408</v>
+      </c>
+      <c r="B409" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C409" t="n">
+        <v>0.02524</v>
+      </c>
+      <c r="D409" t="n">
+        <v>0.02524</v>
+      </c>
+      <c r="E409" t="n">
+        <v>32.152</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>409</v>
+      </c>
+      <c r="B410" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C410" t="n">
+        <v>0.0258</v>
+      </c>
+      <c r="D410" t="n">
+        <v>0.0258</v>
+      </c>
+      <c r="E410" t="n">
+        <v>32.086</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>410</v>
+      </c>
+      <c r="B411" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C411" t="n">
+        <v>0.02551</v>
+      </c>
+      <c r="D411" t="n">
+        <v>0.02551</v>
+      </c>
+      <c r="E411" t="n">
+        <v>32.123</v>
       </c>
     </row>
   </sheetData>
